--- a/Datos_Modificados_Qca.xlsx
+++ b/Datos_Modificados_Qca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\minicores\R_analisis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB6EE56-F2A7-4DCD-ACFE-027CA1EDB939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083A9CD4-6D53-455A-B531-3536BB196105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-705" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2Feb21" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,19 @@
     <sheet name="1Abr2021" sheetId="3" r:id="rId3"/>
     <sheet name="15Abr2021" sheetId="4" r:id="rId4"/>
     <sheet name="29Abr21" sheetId="5" r:id="rId5"/>
-    <sheet name="10Jun2021" sheetId="6" r:id="rId6"/>
-    <sheet name="22Jul2021" sheetId="7" r:id="rId7"/>
-    <sheet name="10AGOS_FENO" sheetId="8" r:id="rId8"/>
-    <sheet name="26Aug21" sheetId="16" r:id="rId9"/>
-    <sheet name="9Sep2021" sheetId="9" r:id="rId10"/>
-    <sheet name="14Oct2021" sheetId="10" r:id="rId11"/>
-    <sheet name="18Nov2021" sheetId="11" r:id="rId12"/>
-    <sheet name="16Dic2021" sheetId="12" r:id="rId13"/>
-    <sheet name="19Ene22" sheetId="13" r:id="rId14"/>
-    <sheet name="8Feb22" sheetId="14" r:id="rId15"/>
-    <sheet name="ray_area" sheetId="15" r:id="rId16"/>
+    <sheet name="13May2021" sheetId="17" r:id="rId6"/>
+    <sheet name="27May2021" sheetId="18" r:id="rId7"/>
+    <sheet name="10Jun2021" sheetId="6" r:id="rId8"/>
+    <sheet name="22Jul2021" sheetId="7" r:id="rId9"/>
+    <sheet name="10AGOS_FENO" sheetId="8" r:id="rId10"/>
+    <sheet name="26Aug21" sheetId="16" r:id="rId11"/>
+    <sheet name="9Sep2021" sheetId="9" r:id="rId12"/>
+    <sheet name="14Oct2021" sheetId="10" r:id="rId13"/>
+    <sheet name="18Nov2021" sheetId="11" r:id="rId14"/>
+    <sheet name="16Dic2021" sheetId="12" r:id="rId15"/>
+    <sheet name="19Ene22" sheetId="13" r:id="rId16"/>
+    <sheet name="8Feb22" sheetId="14" r:id="rId17"/>
+    <sheet name="ray_area" sheetId="15" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,6 +42,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -84,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="208">
   <si>
     <t>Finca</t>
   </si>
@@ -410,9 +415,6 @@
     <t>47QcS10J21</t>
   </si>
   <si>
-    <t>52QcS10J21</t>
-  </si>
-  <si>
     <t>2QcC22J21</t>
   </si>
   <si>
@@ -708,6 +710,9 @@
   </si>
   <si>
     <t>992.5</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1198,9 +1203,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1343,6 +1345,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1771,7 +1782,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>12</v>
@@ -2788,6 +2799,1955 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" ht="36" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="L1" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="67">
+        <v>1</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="69">
+        <v>1</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="52"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+    </row>
+    <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="67">
+        <v>1</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="69">
+        <v>2</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="71">
+        <v>11</v>
+      </c>
+      <c r="H3" s="52">
+        <v>0.48</v>
+      </c>
+      <c r="I3" s="71">
+        <v>0.51</v>
+      </c>
+      <c r="J3" s="52">
+        <v>0.71</v>
+      </c>
+      <c r="K3" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="71"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="67">
+        <v>1</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="69">
+        <v>3</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="74">
+        <v>28</v>
+      </c>
+      <c r="H4" s="75">
+        <v>1.62</v>
+      </c>
+      <c r="I4" s="74">
+        <v>1.5</v>
+      </c>
+      <c r="J4" s="75">
+        <v>1.46</v>
+      </c>
+      <c r="K4" s="74">
+        <v>1.94</v>
+      </c>
+      <c r="L4" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="71"/>
+    </row>
+    <row r="5" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="67">
+        <v>1</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="69">
+        <v>5</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="74">
+        <v>44</v>
+      </c>
+      <c r="H5" s="75">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I5" s="74">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="J5" s="75">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K5" s="74">
+        <v>1.26</v>
+      </c>
+      <c r="L5" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="71"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="67">
+        <v>1</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="69">
+        <v>6</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="76"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="70"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="67">
+        <v>1</v>
+      </c>
+      <c r="C7" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="69">
+        <v>7</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="72"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="77"/>
+    </row>
+    <row r="8" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="67">
+        <v>2</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="69">
+        <v>8</v>
+      </c>
+      <c r="E8" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="74">
+        <v>28</v>
+      </c>
+      <c r="H8" s="74">
+        <v>0.79</v>
+      </c>
+      <c r="I8" s="74">
+        <v>0.86</v>
+      </c>
+      <c r="J8" s="75">
+        <v>0.82</v>
+      </c>
+      <c r="K8" s="74">
+        <v>1.28</v>
+      </c>
+      <c r="L8" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="77"/>
+    </row>
+    <row r="9" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="67">
+        <v>2</v>
+      </c>
+      <c r="C9" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="69">
+        <v>9</v>
+      </c>
+      <c r="E9" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="74">
+        <v>28</v>
+      </c>
+      <c r="H9" s="75">
+        <v>0.85</v>
+      </c>
+      <c r="I9" s="74">
+        <v>0.86</v>
+      </c>
+      <c r="J9" s="75">
+        <v>0.8</v>
+      </c>
+      <c r="K9" s="74">
+        <v>0.9</v>
+      </c>
+      <c r="L9" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9" s="77"/>
+    </row>
+    <row r="10" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="67">
+        <v>2</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="69">
+        <v>10</v>
+      </c>
+      <c r="E10" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="74">
+        <v>48</v>
+      </c>
+      <c r="H10" s="75">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I10" s="74">
+        <v>1</v>
+      </c>
+      <c r="J10" s="75">
+        <v>1.05</v>
+      </c>
+      <c r="K10" s="74">
+        <v>1.2</v>
+      </c>
+      <c r="L10" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" s="77"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="67">
+        <v>2</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="69">
+        <v>11</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="72"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="77"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="67">
+        <v>2</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="69">
+        <v>13</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="72"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="77"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="67">
+        <v>2</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="69">
+        <v>14</v>
+      </c>
+      <c r="E13" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="72"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="77"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="67">
+        <v>3</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="69">
+        <v>17</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="72"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="77"/>
+    </row>
+    <row r="15" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="67">
+        <v>3</v>
+      </c>
+      <c r="C15" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="69">
+        <v>18</v>
+      </c>
+      <c r="E15" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="72" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="71">
+        <v>29</v>
+      </c>
+      <c r="H15" s="75">
+        <v>1.99</v>
+      </c>
+      <c r="I15" s="74">
+        <v>1.79</v>
+      </c>
+      <c r="J15" s="75">
+        <v>1.88</v>
+      </c>
+      <c r="K15" s="74">
+        <v>1.94</v>
+      </c>
+      <c r="L15" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="77"/>
+    </row>
+    <row r="16" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="67">
+        <v>3</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="69">
+        <v>19</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="74">
+        <v>27</v>
+      </c>
+      <c r="H16" s="52">
+        <v>1.85</v>
+      </c>
+      <c r="I16" s="74">
+        <v>1.86</v>
+      </c>
+      <c r="J16" s="75">
+        <v>1.79</v>
+      </c>
+      <c r="K16" s="74">
+        <v>1.56</v>
+      </c>
+      <c r="L16" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="77"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="67">
+        <v>3</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="69">
+        <v>20</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="72"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="70"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="67">
+        <v>4</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="69">
+        <v>23</v>
+      </c>
+      <c r="E18" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="72"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="74"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="77"/>
+    </row>
+    <row r="19" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="67">
+        <v>4</v>
+      </c>
+      <c r="C19" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="69">
+        <v>26</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="74"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="77"/>
+    </row>
+    <row r="20" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="67">
+        <v>4</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="69">
+        <v>30</v>
+      </c>
+      <c r="E20" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="72" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="74">
+        <v>48</v>
+      </c>
+      <c r="H20" s="75">
+        <v>1.41</v>
+      </c>
+      <c r="I20" s="74">
+        <v>1.37</v>
+      </c>
+      <c r="J20" s="75">
+        <v>1.37</v>
+      </c>
+      <c r="K20" s="74">
+        <v>1.67</v>
+      </c>
+      <c r="L20" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" s="74"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="67">
+        <v>4</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="69">
+        <v>31</v>
+      </c>
+      <c r="E21" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="72"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="77"/>
+    </row>
+    <row r="22" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="67">
+        <v>5</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="69">
+        <v>36</v>
+      </c>
+      <c r="E22" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="74">
+        <v>20</v>
+      </c>
+      <c r="H22" s="75">
+        <v>0.51</v>
+      </c>
+      <c r="I22" s="74">
+        <v>0.44</v>
+      </c>
+      <c r="J22" s="75">
+        <v>0.51</v>
+      </c>
+      <c r="K22" s="74">
+        <v>0.44</v>
+      </c>
+      <c r="L22" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" s="77"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="67">
+        <v>5</v>
+      </c>
+      <c r="C23" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="69">
+        <v>37</v>
+      </c>
+      <c r="E23" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="72"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="74"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="77"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="67">
+        <v>5</v>
+      </c>
+      <c r="C24" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="69">
+        <v>38</v>
+      </c>
+      <c r="E24" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="72"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="77"/>
+    </row>
+    <row r="25" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="67">
+        <v>5</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="69">
+        <v>40</v>
+      </c>
+      <c r="E25" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="74">
+        <v>44</v>
+      </c>
+      <c r="H25" s="75">
+        <v>1.04</v>
+      </c>
+      <c r="I25" s="74">
+        <v>1.06</v>
+      </c>
+      <c r="J25" s="75">
+        <v>1.08</v>
+      </c>
+      <c r="K25" s="74"/>
+      <c r="L25" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="M25" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" s="77"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="67">
+        <v>5</v>
+      </c>
+      <c r="C26" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="69">
+        <v>43</v>
+      </c>
+      <c r="E26" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="72"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="77"/>
+    </row>
+    <row r="27" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="67">
+        <v>5</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="69">
+        <v>44</v>
+      </c>
+      <c r="E27" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="74">
+        <v>35</v>
+      </c>
+      <c r="H27" s="75">
+        <v>0.62</v>
+      </c>
+      <c r="I27" s="74">
+        <v>0.59</v>
+      </c>
+      <c r="J27" s="75">
+        <v>0.53</v>
+      </c>
+      <c r="K27" s="74">
+        <v>0.64</v>
+      </c>
+      <c r="L27" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M27" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" s="77"/>
+    </row>
+    <row r="28" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="67">
+        <v>6</v>
+      </c>
+      <c r="C28" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="69">
+        <v>47</v>
+      </c>
+      <c r="E28" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="74"/>
+      <c r="H28" s="75">
+        <v>2.74</v>
+      </c>
+      <c r="I28" s="74">
+        <v>3.47</v>
+      </c>
+      <c r="J28" s="75">
+        <v>3.14</v>
+      </c>
+      <c r="K28" s="74">
+        <v>3.3</v>
+      </c>
+      <c r="L28" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" s="77"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="67">
+        <v>6</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="69">
+        <v>51</v>
+      </c>
+      <c r="E29" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="72"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="75"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="75"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="77"/>
+    </row>
+    <row r="30" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="67">
+        <v>6</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="69">
+        <v>52</v>
+      </c>
+      <c r="E30" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="72" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30" s="78">
+        <v>12</v>
+      </c>
+      <c r="H30" s="79">
+        <v>0.27</v>
+      </c>
+      <c r="I30" s="78">
+        <v>0.26</v>
+      </c>
+      <c r="J30" s="79">
+        <v>0.4</v>
+      </c>
+      <c r="K30" s="78">
+        <v>0.44</v>
+      </c>
+      <c r="L30" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="M30" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" s="80"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="82">
+        <v>6</v>
+      </c>
+      <c r="C31" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="84">
+        <v>55</v>
+      </c>
+      <c r="E31" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="85"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="87"/>
+      <c r="M31" s="86"/>
+      <c r="N31" s="88"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C86517-B91B-4061-867D-8EB3BAD5F5CB}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L1" s="55" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="100"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="101"/>
+      <c r="H3" s="102">
+        <v>0.69</v>
+      </c>
+      <c r="I3" s="101">
+        <v>0.72</v>
+      </c>
+      <c r="J3" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="K3" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="L3" s="101" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7">
+        <v>3</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="103"/>
+      <c r="H4" s="104">
+        <v>1.25</v>
+      </c>
+      <c r="I4" s="103">
+        <v>1.27</v>
+      </c>
+      <c r="J4" s="104">
+        <v>1.4</v>
+      </c>
+      <c r="K4" s="104">
+        <v>1.4</v>
+      </c>
+      <c r="L4" s="113">
+        <v>2410021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="103"/>
+      <c r="H5" s="104">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I5" s="103">
+        <v>0.44</v>
+      </c>
+      <c r="J5" s="104">
+        <v>0.21</v>
+      </c>
+      <c r="K5" s="104">
+        <v>0.21</v>
+      </c>
+      <c r="L5" s="101"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="101"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="100"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5">
+        <v>7</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="105"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7">
+        <v>8</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="29"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="103"/>
+      <c r="L8" s="105"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7">
+        <v>9</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="103"/>
+      <c r="H9" s="104">
+        <v>1.06</v>
+      </c>
+      <c r="I9" s="103">
+        <v>0.99</v>
+      </c>
+      <c r="J9" s="104">
+        <v>1.01</v>
+      </c>
+      <c r="K9" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="L9" s="105"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="7">
+        <v>10</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="103"/>
+      <c r="H10" s="104">
+        <v>0.93</v>
+      </c>
+      <c r="I10" s="103">
+        <v>0.69</v>
+      </c>
+      <c r="J10" s="104">
+        <v>0.97</v>
+      </c>
+      <c r="K10" s="104">
+        <v>1.4</v>
+      </c>
+      <c r="L10" s="105"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5">
+        <v>11</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="105"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="5">
+        <v>13</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="105"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5">
+        <v>14</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="103"/>
+      <c r="L13" s="105"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>17</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="105"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="7">
+        <v>18</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="G15" s="102"/>
+      <c r="H15" s="101">
+        <v>1.99</v>
+      </c>
+      <c r="I15" s="104">
+        <v>1.79</v>
+      </c>
+      <c r="J15" s="101">
+        <v>1.88</v>
+      </c>
+      <c r="K15" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="L15" s="105"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="7">
+        <v>19</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="102">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="I16" s="106">
+        <v>2</v>
+      </c>
+      <c r="J16" s="104">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K16" s="104">
+        <v>1.4</v>
+      </c>
+      <c r="L16" s="105"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="5">
+        <v>20</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="100"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5">
+        <v>23</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="105"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3">
+        <v>4</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="7">
+        <v>26</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="103"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="103"/>
+      <c r="L19" s="105"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="7">
+        <v>30</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="G20" s="103"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="5">
+        <v>31</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="103"/>
+      <c r="L21" s="105"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3">
+        <v>5</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7">
+        <v>36</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="103"/>
+      <c r="H22" s="104">
+        <v>0.71</v>
+      </c>
+      <c r="I22" s="103">
+        <v>0.54</v>
+      </c>
+      <c r="J22" s="104">
+        <v>0.52</v>
+      </c>
+      <c r="K22" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="L22" s="105"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="3">
+        <v>5</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5">
+        <v>37</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="105"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="5">
+        <v>38</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="105"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="3">
+        <v>5</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="7">
+        <v>40</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="103"/>
+      <c r="H25" s="104">
+        <v>0.88</v>
+      </c>
+      <c r="I25" s="103">
+        <v>0.87</v>
+      </c>
+      <c r="J25" s="104">
+        <v>0.9</v>
+      </c>
+      <c r="K25" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="L25" s="105"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5">
+        <v>43</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="102"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="7">
+        <v>44</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="103"/>
+      <c r="H27" s="104">
+        <v>0.49</v>
+      </c>
+      <c r="I27" s="103">
+        <v>0.48</v>
+      </c>
+      <c r="J27" s="103">
+        <v>0.5</v>
+      </c>
+      <c r="K27" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="L27" s="105"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="3">
+        <v>6</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="7">
+        <v>47</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="103"/>
+      <c r="H28" s="104">
+        <v>0.8</v>
+      </c>
+      <c r="I28" s="103">
+        <v>0.9</v>
+      </c>
+      <c r="J28" s="104">
+        <v>1</v>
+      </c>
+      <c r="K28" s="104">
+        <v>1.4</v>
+      </c>
+      <c r="L28" s="105"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="3">
+        <v>6</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="5">
+        <v>51</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="103"/>
+      <c r="L29" s="105"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3">
+        <v>6</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="7">
+        <v>52</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="107"/>
+      <c r="H30" s="108">
+        <v>0.67</v>
+      </c>
+      <c r="I30" s="107">
+        <v>0.8</v>
+      </c>
+      <c r="J30" s="108">
+        <v>0.64</v>
+      </c>
+      <c r="K30" s="101">
+        <v>0.65</v>
+      </c>
+      <c r="L30" s="109"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="35">
+        <v>6</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="37">
+        <v>55</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="38"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="112"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2824,10 +4784,10 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2869,7 +4829,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G3" s="28">
         <v>24</v>
@@ -2905,7 +4865,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G4" s="12">
         <v>52</v>
@@ -2941,7 +4901,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G5" s="12">
         <v>46</v>
@@ -3025,7 +4985,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G8">
         <v>61</v>
@@ -3063,7 +5023,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G9" s="12">
         <v>22</v>
@@ -3101,7 +5061,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G10" s="12">
         <v>30</v>
@@ -3235,7 +5195,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G15">
         <v>41</v>
@@ -3273,12 +5233,12 @@
         <v>16</v>
       </c>
       <c r="F16" s="29"/>
-      <c r="G16" s="90"/>
+      <c r="G16" s="89"/>
       <c r="H16" s="52"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="90"/>
-      <c r="L16" s="78"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="89"/>
+      <c r="L16" s="77"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
@@ -3344,14 +5304,14 @@
         <v>16</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G19" s="12">
         <v>9</v>
       </c>
-      <c r="H19" s="98"/>
-      <c r="I19" s="99"/>
-      <c r="J19" s="98"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="97"/>
       <c r="K19" s="12">
         <v>0.499</v>
       </c>
@@ -3376,7 +5336,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G20" s="12">
         <v>29</v>
@@ -3438,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G22" s="12">
         <v>19</v>
@@ -3524,7 +5484,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G25" s="12">
         <v>34</v>
@@ -3585,7 +5545,7 @@
         <v>16</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G27" s="12">
         <v>49</v>
@@ -3623,14 +5583,14 @@
         <v>16</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G28" s="12">
         <v>21</v>
       </c>
-      <c r="H28" s="98"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="98"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="97"/>
       <c r="K28" s="12">
         <v>0.47599999999999998</v>
       </c>
@@ -3679,12 +5639,12 @@
         <v>16</v>
       </c>
       <c r="F30" s="29"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="81"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="59" t="s">
@@ -3720,7 +5680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3761,10 +5721,10 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M1" s="55" t="s">
         <v>8</v>
@@ -3809,7 +5769,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G3" s="28">
         <v>5</v>
@@ -3848,7 +5808,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G4" s="12">
         <v>33</v>
@@ -3960,7 +5920,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="12">
         <v>22</v>
@@ -3999,7 +5959,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G9" s="12">
         <v>26</v>
@@ -4038,7 +5998,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G10" s="12">
         <v>38</v>
@@ -4177,7 +6137,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G15" s="28">
         <v>24</v>
@@ -4289,7 +6249,7 @@
         <v>16</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G19" s="12">
         <v>21</v>
@@ -4328,7 +6288,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G20" s="12">
         <v>18</v>
@@ -4392,7 +6352,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G22" s="12">
         <v>35</v>
@@ -4481,7 +6441,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G25" s="12">
         <v>23</v>
@@ -4570,7 +6530,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G28" s="12">
         <v>38</v>
@@ -4634,7 +6594,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G30" s="50">
         <v>24</v>
@@ -4687,7 +6647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4728,10 +6688,10 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M1" s="55" t="s">
         <v>8</v>
@@ -4777,7 +6737,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G3" s="28">
         <v>32</v>
@@ -4816,7 +6776,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G4" s="12">
         <v>27</v>
@@ -4869,7 +6829,7 @@
       <c r="L5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="91"/>
+      <c r="M5" s="90"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
@@ -4936,14 +6896,14 @@
         <v>16</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G8" s="12">
         <v>18</v>
       </c>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="97"/>
       <c r="K8" s="12">
         <v>0.61</v>
       </c>
@@ -4969,7 +6929,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G9" s="12">
         <v>30</v>
@@ -5008,7 +6968,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G10" s="12">
         <v>12</v>
@@ -5147,7 +7107,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G15" s="28">
         <v>44</v>
@@ -5186,7 +7146,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G16" s="12">
         <v>38</v>
@@ -5299,14 +7259,14 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G20" s="12">
         <v>25</v>
       </c>
-      <c r="H20" s="98"/>
-      <c r="I20" s="99"/>
-      <c r="J20" s="98"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="97"/>
       <c r="K20" s="12">
         <v>1.1499999999999999</v>
       </c>
@@ -5357,14 +7317,14 @@
         <v>16</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G22" s="12">
         <v>25</v>
       </c>
-      <c r="H22" s="98"/>
-      <c r="I22" s="99"/>
-      <c r="J22" s="98"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="97"/>
       <c r="K22" s="12">
         <v>0.42</v>
       </c>
@@ -5440,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G25" s="12">
         <v>42</v>
@@ -5529,7 +7489,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G28" s="12">
         <v>34</v>
@@ -5593,7 +7553,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="29"/>
-      <c r="G30" s="92"/>
+      <c r="G30" s="91"/>
       <c r="H30" s="48"/>
       <c r="I30" s="50"/>
       <c r="J30" s="48"/>
@@ -5632,7 +7592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5672,10 +7632,10 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M1" s="55" t="s">
         <v>8</v>
@@ -5721,7 +7681,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G3" s="28">
         <v>31</v>
@@ -5739,7 +7699,7 @@
         <v>1.23</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M3" s="28"/>
     </row>
@@ -5760,7 +7720,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G4" s="12">
         <v>52</v>
@@ -5778,7 +7738,7 @@
         <v>1.71</v>
       </c>
       <c r="L4" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M4" s="28"/>
     </row>
@@ -5872,7 +7832,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G8" s="12">
         <v>74</v>
@@ -5936,7 +7896,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G10" s="12">
         <v>36</v>
@@ -6075,7 +8035,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G15" s="28">
         <v>55</v>
@@ -6114,7 +8074,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G16" s="12">
         <v>55</v>
@@ -6227,7 +8187,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G20" s="12">
         <v>28</v>
@@ -6291,7 +8251,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G22" s="12">
         <v>28</v>
@@ -6430,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G27" s="12">
         <v>6</v>
@@ -6469,7 +8429,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G28" s="12">
         <v>34</v>
@@ -6533,7 +8493,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G30" s="50">
         <v>25</v>
@@ -6590,7 +8550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6630,13 +8590,13 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M1" s="55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6678,7 +8638,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G3" s="28">
         <v>45</v>
@@ -6719,7 +8679,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G4" s="12">
         <v>60</v>
@@ -6760,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G5" s="12">
         <v>40</v>
@@ -6849,13 +8809,13 @@
         <v>16</v>
       </c>
       <c r="F8" s="29"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="78"/>
+      <c r="G8" s="89"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="89"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
+      <c r="M8" s="77"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
@@ -6874,7 +8834,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G9" s="12">
         <v>34</v>
@@ -6915,7 +8875,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G10" s="12">
         <v>41</v>
@@ -7056,9 +9016,9 @@
         <v>16</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="G15" s="93">
+        <v>179</v>
+      </c>
+      <c r="G15" s="92">
         <v>37</v>
       </c>
       <c r="H15" s="12">
@@ -7097,7 +9057,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G16" s="12">
         <v>70</v>
@@ -7120,7 +9080,7 @@
       <c r="M16" s="47">
         <v>865.05780000000004</v>
       </c>
-      <c r="O16" s="100"/>
+      <c r="O16" s="99"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
@@ -7188,13 +9148,13 @@
         <v>16</v>
       </c>
       <c r="F19" s="29"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="78"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="77"/>
     </row>
     <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56" t="s">
@@ -7213,7 +9173,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G20" s="12">
         <v>25</v>
@@ -7273,7 +9233,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G22" s="12">
         <v>11</v>
@@ -7362,7 +9322,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G25" s="12">
         <v>30</v>
@@ -7428,14 +9388,14 @@
         <v>16</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G27" s="12">
         <v>46</v>
       </c>
-      <c r="H27" s="98"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="98"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="98"/>
+      <c r="J27" s="97"/>
       <c r="K27" s="12">
         <v>0.58399999999999996</v>
       </c>
@@ -7463,7 +9423,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G28" s="12">
         <v>26</v>
@@ -7529,7 +9489,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G30" s="50">
         <v>34</v>
@@ -7588,7 +9548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7628,10 +9588,10 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M1" s="55" t="s">
         <v>8</v>
@@ -7677,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G3" s="28">
         <v>27</v>
@@ -7716,7 +9676,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G4" s="12">
         <v>92</v>
@@ -7755,7 +9715,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G5" s="12">
         <v>39</v>
@@ -7843,7 +9803,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G8" s="12">
         <v>28</v>
@@ -7907,7 +9867,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G10" s="12">
         <v>30</v>
@@ -8046,7 +10006,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="29"/>
-      <c r="G15" s="91"/>
+      <c r="G15" s="90"/>
       <c r="H15" s="8"/>
       <c r="I15" s="12"/>
       <c r="J15" s="8"/>
@@ -8071,7 +10031,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G16" s="12">
         <v>55</v>
@@ -8184,7 +10144,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G20" s="12">
         <v>57</v>
@@ -8321,7 +10281,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G25" s="12">
         <v>29</v>
@@ -8385,7 +10345,7 @@
         <v>16</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G27" s="12">
         <v>36</v>
@@ -8474,7 +10434,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G30" s="50">
         <v>54</v>
@@ -8531,7 +10491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8555,20 +10515,20 @@
       <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="94" t="s">
+      <c r="G1" s="93" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="94" t="s">
-        <v>204</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="95"/>
+      <c r="A2" s="94"/>
       <c r="B2" s="8"/>
-      <c r="C2" s="96"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="96"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="56" t="s">
@@ -8604,7 +10564,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G4">
         <v>0.56746399999999997</v>
@@ -8630,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -8656,7 +10616,7 @@
         <v>16</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -8718,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G9">
         <v>3.5099999999999992E-2</v>
@@ -8744,7 +10704,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G10">
         <v>0.23200000000000001</v>
@@ -8770,7 +10730,7 @@
         <v>16</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -8868,7 +10828,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G16">
         <v>0.53510333333333326</v>
@@ -8894,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G17">
         <v>0.69607333333333332</v>
@@ -8956,7 +10916,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G20">
         <v>0.34104000000000001</v>
@@ -8982,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G21">
         <v>0.60892666666666673</v>
@@ -9026,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H23">
         <v>0.25029333333333337</v>
@@ -9085,7 +11045,7 @@
         <v>16</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -9129,7 +11089,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -9155,7 +11115,7 @@
         <v>16</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G29">
         <v>1.9659266666666666</v>
@@ -9199,7 +11159,7 @@
         <v>16</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -9277,7 +11237,7 @@
         <v>11</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>12</v>
@@ -10284,7 +12244,7 @@
         <v>11</v>
       </c>
       <c r="K1" s="43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="44" t="s">
         <v>12</v>
@@ -10339,7 +12299,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G3" s="47">
         <v>0</v>
@@ -11444,7 +13404,7 @@
         <v>11</v>
       </c>
       <c r="K1" s="43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="54" t="s">
         <v>12</v>
@@ -12565,7 +14525,7 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="54" t="s">
         <v>12</v>
@@ -13507,7 +15467,7 @@
         <v>18</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="O27" s="47"/>
     </row>
@@ -13551,8 +15511,8 @@
       <c r="M28" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="N28" s="28" t="s">
-        <v>37</v>
+      <c r="N28" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="O28" s="47"/>
     </row>
@@ -13662,15 +15622,2110 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E713CF5-3ADC-4FA2-AC32-4B11FD527DB8}">
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="11.42578125" style="102"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K1" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="114" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="46"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="28">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>0.34</v>
+      </c>
+      <c r="H3" s="28">
+        <v>0.27</v>
+      </c>
+      <c r="I3">
+        <v>0.24</v>
+      </c>
+      <c r="J3" s="28">
+        <v>0.36</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="28"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7">
+        <v>3</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="12">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="J4" s="47">
+        <v>0.41</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="28"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="12">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0.47</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="28"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="14"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="46"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5">
+        <v>7</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="47"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7">
+        <v>8</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="33"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="47"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7">
+        <v>9</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="12">
+        <v>4</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="7">
+        <v>10</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="12">
+        <v>2</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0.13</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5">
+        <v>11</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="5">
+        <v>13</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5">
+        <v>14</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>17</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="103"/>
+      <c r="N14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="7">
+        <v>18</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="28">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>0.37</v>
+      </c>
+      <c r="H15" s="46">
+        <v>0.37</v>
+      </c>
+      <c r="I15" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="28">
+        <v>0.41</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="7">
+        <v>19</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="12">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>0.37</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.44</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0.38</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="47"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="5">
+        <v>20</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="14"/>
+      <c r="M17" s="101"/>
+      <c r="N17" s="46"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5">
+        <v>23</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="47"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3">
+        <v>4</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="7">
+        <v>26</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="12">
+        <v>2</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="J19" s="12">
+        <v>0.23</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="47"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="7">
+        <v>30</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="12">
+        <v>2</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="H20" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0.19</v>
+      </c>
+      <c r="J20" s="12">
+        <v>0.27</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="5">
+        <v>31</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="47"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3">
+        <v>5</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7">
+        <v>36</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="12">
+        <v>4</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="H22" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="J22" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="47"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="3">
+        <v>5</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5">
+        <v>37</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="47"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="5">
+        <v>38</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="3">
+        <v>5</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="7">
+        <v>40</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="12">
+        <v>3</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H25" s="12">
+        <v>0.27</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="J25" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="M25" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="47"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5">
+        <v>43</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="47"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="7">
+        <v>44</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="12">
+        <v>2</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="J27" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M27" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="3">
+        <v>6</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="7">
+        <v>47</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="12">
+        <v>5</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="H28" s="12">
+        <v>0.36</v>
+      </c>
+      <c r="I28" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="J28" s="12">
+        <v>0.35</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" s="47"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="3">
+        <v>6</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="5">
+        <v>51</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="103"/>
+      <c r="N29" s="47"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3">
+        <v>6</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="7">
+        <v>52</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="50">
+        <v>5</v>
+      </c>
+      <c r="G30" s="48">
+        <v>0.27</v>
+      </c>
+      <c r="H30" s="50">
+        <v>0.22</v>
+      </c>
+      <c r="I30" s="48">
+        <v>0.3</v>
+      </c>
+      <c r="J30" s="50">
+        <v>0.23</v>
+      </c>
+      <c r="K30" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="M30" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="35">
+        <v>6</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="37">
+        <v>55</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="110"/>
+      <c r="N31" s="51"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931120A9-A2F6-4764-B72D-C990598ADC87}">
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="11.42578125" style="102"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K1" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="114" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="46"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="28">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>0.34</v>
+      </c>
+      <c r="H3" s="28">
+        <v>0.27</v>
+      </c>
+      <c r="I3">
+        <v>0.24</v>
+      </c>
+      <c r="J3" s="28">
+        <v>0.36</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="28"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7">
+        <v>3</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="12">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="J4" s="47">
+        <v>0.41</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="28"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="12">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0.47</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="28"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="14"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="46"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5">
+        <v>7</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="47"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7">
+        <v>8</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="33">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.31</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0.31</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0.38</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0.35</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="47"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7">
+        <v>9</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="12">
+        <v>4</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="7">
+        <v>10</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="12">
+        <v>2</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0.13</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5">
+        <v>11</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="5">
+        <v>13</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5">
+        <v>14</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>17</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="103"/>
+      <c r="N14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="7">
+        <v>18</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="28">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>0.37</v>
+      </c>
+      <c r="H15" s="46">
+        <v>0.37</v>
+      </c>
+      <c r="I15" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="28">
+        <v>0.41</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="7">
+        <v>19</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="12">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>0.37</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.44</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0.38</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="47"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="5">
+        <v>20</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="14"/>
+      <c r="M17" s="101"/>
+      <c r="N17" s="46"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5">
+        <v>23</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="47"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3">
+        <v>4</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="7">
+        <v>26</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="47"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="7">
+        <v>30</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="12">
+        <v>2</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="H20" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0.19</v>
+      </c>
+      <c r="J20" s="12">
+        <v>0.27</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="5">
+        <v>31</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="47"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3">
+        <v>5</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7">
+        <v>36</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="12">
+        <v>4</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="H22" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="J22" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" s="47"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="3">
+        <v>5</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5">
+        <v>37</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="47"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="5">
+        <v>38</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="3">
+        <v>5</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="7">
+        <v>40</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="12">
+        <v>3</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H25" s="12">
+        <v>0.27</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="J25" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" s="47"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5">
+        <v>43</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="47"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="7">
+        <v>44</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="12">
+        <v>2</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="J27" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="3">
+        <v>6</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="7">
+        <v>47</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="47"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="3">
+        <v>6</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="5">
+        <v>51</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="103"/>
+      <c r="N29" s="47"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3">
+        <v>6</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="7">
+        <v>52</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="50">
+        <v>5</v>
+      </c>
+      <c r="G30" s="48">
+        <v>0.27</v>
+      </c>
+      <c r="H30" s="50">
+        <v>0.22</v>
+      </c>
+      <c r="I30" s="48">
+        <v>0.3</v>
+      </c>
+      <c r="J30" s="50">
+        <v>0.23</v>
+      </c>
+      <c r="K30" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="M30" s="101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="35">
+        <v>6</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="37">
+        <v>55</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="110"/>
+      <c r="N31" s="51"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" style="102"/>
     <col min="1016" max="1024" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -13702,7 +17757,7 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="54" t="s">
         <v>12</v>
@@ -13716,8 +17771,9 @@
       <c r="O1" s="55" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="114"/>
+    </row>
+    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
         <v>13</v>
       </c>
@@ -13741,8 +17797,9 @@
       <c r="M2" s="46"/>
       <c r="N2" s="46"/>
       <c r="O2" s="46"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="100"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="56" t="s">
         <v>13</v>
       </c>
@@ -13786,8 +17843,9 @@
         <v>37</v>
       </c>
       <c r="O3" s="28"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="101"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="56" t="s">
         <v>13</v>
       </c>
@@ -13828,11 +17886,12 @@
         <v>37</v>
       </c>
       <c r="N4" s="28" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O4" s="28"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="101"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
         <v>13</v>
       </c>
@@ -13872,12 +17931,13 @@
       <c r="M5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="12" t="s">
-        <v>18</v>
+      <c r="N5" s="28" t="s">
+        <v>37</v>
       </c>
       <c r="O5" s="28"/>
-    </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="101"/>
+    </row>
+    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
         <v>13</v>
       </c>
@@ -13900,8 +17960,9 @@
       <c r="L6" s="14"/>
       <c r="N6" s="28"/>
       <c r="O6" s="46"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="101"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="56" t="s">
         <v>13</v>
       </c>
@@ -13927,8 +17988,9 @@
       <c r="M7" s="8"/>
       <c r="N7" s="12"/>
       <c r="O7" s="47"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="103"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
         <v>13</v>
       </c>
@@ -13972,8 +18034,9 @@
         <v>37</v>
       </c>
       <c r="O8" s="47"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="103"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
         <v>13</v>
       </c>
@@ -14017,8 +18080,9 @@
         <v>18</v>
       </c>
       <c r="O9" s="47"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="101"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="56" t="s">
         <v>13</v>
       </c>
@@ -14059,11 +18123,12 @@
         <v>37</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O10" s="47"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="103"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
         <v>13</v>
       </c>
@@ -14089,8 +18154,9 @@
       <c r="M11" s="8"/>
       <c r="N11" s="12"/>
       <c r="O11" s="47"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="103"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="56" t="s">
         <v>13</v>
       </c>
@@ -14116,8 +18182,9 @@
       <c r="M12" s="8"/>
       <c r="N12" s="12"/>
       <c r="O12" s="47"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="103"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
         <v>13</v>
       </c>
@@ -14143,8 +18210,9 @@
       <c r="M13" s="8"/>
       <c r="N13" s="12"/>
       <c r="O13" s="47"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="103"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="56" t="s">
         <v>13</v>
       </c>
@@ -14170,8 +18238,9 @@
       <c r="M14" s="8"/>
       <c r="N14" s="12"/>
       <c r="O14" s="47"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="103"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
         <v>13</v>
       </c>
@@ -14215,8 +18284,9 @@
         <v>37</v>
       </c>
       <c r="O15" s="47"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="101"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="56" t="s">
         <v>13</v>
       </c>
@@ -14260,8 +18330,9 @@
         <v>37</v>
       </c>
       <c r="O16" s="47"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="101"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
         <v>13</v>
       </c>
@@ -14285,8 +18356,9 @@
       <c r="L17" s="14"/>
       <c r="N17" s="28"/>
       <c r="O17" s="46"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="101"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
         <v>13</v>
       </c>
@@ -14312,8 +18384,9 @@
       <c r="M18" s="8"/>
       <c r="N18" s="12"/>
       <c r="O18" s="47"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="103"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="56" t="s">
         <v>13</v>
       </c>
@@ -14339,8 +18412,9 @@
       <c r="M19" s="8"/>
       <c r="N19" s="12"/>
       <c r="O19" s="47"/>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P19" s="103"/>
+    </row>
+    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56" t="s">
         <v>13</v>
       </c>
@@ -14384,8 +18458,9 @@
         <v>37</v>
       </c>
       <c r="O20" s="12"/>
-    </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P20" s="103"/>
+    </row>
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="56" t="s">
         <v>13</v>
       </c>
@@ -14411,8 +18486,9 @@
       <c r="M21" s="8"/>
       <c r="N21" s="12"/>
       <c r="O21" s="47"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="103"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="56" t="s">
         <v>13</v>
       </c>
@@ -14438,8 +18514,9 @@
       <c r="M22" s="8"/>
       <c r="N22" s="12"/>
       <c r="O22" s="47"/>
-    </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="103"/>
+    </row>
+    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="56" t="s">
         <v>13</v>
       </c>
@@ -14465,8 +18542,9 @@
       <c r="M23" s="8"/>
       <c r="N23" s="12"/>
       <c r="O23" s="47"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="103"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="56" t="s">
         <v>13</v>
       </c>
@@ -14492,8 +18570,9 @@
       <c r="M24" s="8"/>
       <c r="N24" s="12"/>
       <c r="O24" s="47"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="103"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="56" t="s">
         <v>13</v>
       </c>
@@ -14534,11 +18613,12 @@
         <v>37</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O25" s="47"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="103"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="56" t="s">
         <v>13</v>
       </c>
@@ -14564,8 +18644,9 @@
       <c r="M26" s="8"/>
       <c r="N26" s="12"/>
       <c r="O26" s="47"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="103"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="56" t="s">
         <v>13</v>
       </c>
@@ -14606,11 +18687,12 @@
         <v>37</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O27" s="47"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="103"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="56" t="s">
         <v>13</v>
       </c>
@@ -14654,8 +18736,9 @@
         <v>37</v>
       </c>
       <c r="O28" s="47"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="103"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="56" t="s">
         <v>13</v>
       </c>
@@ -14671,18 +18754,19 @@
       <c r="E29" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="29"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="12"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="103"/>
+      <c r="L29" s="116"/>
+      <c r="M29" s="104"/>
+      <c r="N29" s="103"/>
       <c r="O29" s="47"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="103"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="56" t="s">
         <v>13</v>
       </c>
@@ -14698,36 +18782,19 @@
       <c r="E30" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="G30" s="60">
-        <v>0</v>
-      </c>
-      <c r="H30" s="17">
-        <v>1.85</v>
-      </c>
-      <c r="I30" s="60">
-        <v>1.69</v>
-      </c>
-      <c r="J30" s="17">
-        <v>1.63</v>
-      </c>
-      <c r="K30" s="60">
-        <v>1.92</v>
-      </c>
-      <c r="L30" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="M30" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="N30" s="60" t="s">
-        <v>18</v>
-      </c>
+      <c r="F30" s="115"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="103"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="103"/>
+      <c r="L30" s="116"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="103"/>
       <c r="O30" s="58"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="101"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="59" t="s">
         <v>13</v>
       </c>
@@ -14753,6 +18820,7 @@
       <c r="M31" s="40"/>
       <c r="N31" s="39"/>
       <c r="O31" s="51"/>
+      <c r="P31" s="110"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14760,7 +18828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14803,7 +18871,7 @@
         <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="53" t="s">
         <v>51</v>
@@ -14856,7 +18924,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="28">
         <v>11</v>
@@ -14898,7 +18966,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="12">
         <v>28</v>
@@ -14940,7 +19008,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G5" s="12">
         <v>44</v>
@@ -15031,7 +19099,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G8" s="12">
         <v>28</v>
@@ -15073,7 +19141,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G9" s="12">
         <v>28</v>
@@ -15115,7 +19183,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G10" s="12">
         <v>48</v>
@@ -15261,7 +19329,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G15" s="28">
         <v>29</v>
@@ -15303,7 +19371,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G16" s="12">
         <v>27</v>
@@ -15421,7 +19489,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G20" s="12">
         <v>48</v>
@@ -15489,7 +19557,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G22" s="12">
         <v>20</v>
@@ -15583,7 +19651,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G25" s="12">
         <v>44</v>
@@ -15649,7 +19717,7 @@
         <v>16</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="12">
         <v>35</v>
@@ -15691,7 +19759,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G28" s="12">
         <v>26</v>
@@ -15759,7 +19827,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G30" s="50">
         <v>12</v>
@@ -15814,1953 +19882,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:O31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:15" ht="36" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="62" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="64" t="s">
-        <v>205</v>
-      </c>
-      <c r="L1" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="N1" s="66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="68">
-        <v>1</v>
-      </c>
-      <c r="C2" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="70">
-        <v>1</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="52"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-    </row>
-    <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="68">
-        <v>1</v>
-      </c>
-      <c r="C3" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="70">
-        <v>2</v>
-      </c>
-      <c r="E3" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="72">
-        <v>11</v>
-      </c>
-      <c r="H3" s="52">
-        <v>0.48</v>
-      </c>
-      <c r="I3" s="72">
-        <v>0.51</v>
-      </c>
-      <c r="J3" s="52">
-        <v>0.71</v>
-      </c>
-      <c r="K3" s="72">
-        <v>0.5</v>
-      </c>
-      <c r="L3" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="72" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" s="72"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="68">
-        <v>1</v>
-      </c>
-      <c r="C4" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="70">
-        <v>3</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="75">
-        <v>28</v>
-      </c>
-      <c r="H4" s="76">
-        <v>1.62</v>
-      </c>
-      <c r="I4" s="75">
-        <v>1.5</v>
-      </c>
-      <c r="J4" s="76">
-        <v>1.46</v>
-      </c>
-      <c r="K4" s="75">
-        <v>1.94</v>
-      </c>
-      <c r="L4" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="72" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="72"/>
-    </row>
-    <row r="5" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="68">
-        <v>1</v>
-      </c>
-      <c r="C5" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="70">
-        <v>5</v>
-      </c>
-      <c r="E5" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="75">
-        <v>44</v>
-      </c>
-      <c r="H5" s="76">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="I5" s="75">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="J5" s="76">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="K5" s="75">
-        <v>1.26</v>
-      </c>
-      <c r="L5" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="72"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="68">
-        <v>1</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="70">
-        <v>6</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="77"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="71"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="68">
-        <v>1</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="70">
-        <v>7</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="73"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="78"/>
-    </row>
-    <row r="8" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="68">
-        <v>2</v>
-      </c>
-      <c r="C8" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="70">
-        <v>8</v>
-      </c>
-      <c r="E8" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="75">
-        <v>28</v>
-      </c>
-      <c r="H8" s="75">
-        <v>0.79</v>
-      </c>
-      <c r="I8" s="75">
-        <v>0.86</v>
-      </c>
-      <c r="J8" s="76">
-        <v>0.82</v>
-      </c>
-      <c r="K8" s="75">
-        <v>1.28</v>
-      </c>
-      <c r="L8" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="78"/>
-    </row>
-    <row r="9" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="68">
-        <v>2</v>
-      </c>
-      <c r="C9" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="70">
-        <v>9</v>
-      </c>
-      <c r="E9" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="73" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="75">
-        <v>28</v>
-      </c>
-      <c r="H9" s="76">
-        <v>0.85</v>
-      </c>
-      <c r="I9" s="75">
-        <v>0.86</v>
-      </c>
-      <c r="J9" s="76">
-        <v>0.8</v>
-      </c>
-      <c r="K9" s="75">
-        <v>0.9</v>
-      </c>
-      <c r="L9" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N9" s="78"/>
-    </row>
-    <row r="10" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="68">
-        <v>2</v>
-      </c>
-      <c r="C10" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="70">
-        <v>10</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="73" t="s">
-        <v>114</v>
-      </c>
-      <c r="G10" s="75">
-        <v>48</v>
-      </c>
-      <c r="H10" s="76">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I10" s="75">
-        <v>1</v>
-      </c>
-      <c r="J10" s="76">
-        <v>1.05</v>
-      </c>
-      <c r="K10" s="75">
-        <v>1.2</v>
-      </c>
-      <c r="L10" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" s="78"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="68">
-        <v>2</v>
-      </c>
-      <c r="C11" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="70">
-        <v>11</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="73"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="76"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="78"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="68">
-        <v>2</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="70">
-        <v>13</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="73"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="75"/>
-      <c r="N12" s="78"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="68">
-        <v>2</v>
-      </c>
-      <c r="C13" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="70">
-        <v>14</v>
-      </c>
-      <c r="E13" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="73"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="75"/>
-      <c r="N13" s="78"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="68">
-        <v>3</v>
-      </c>
-      <c r="C14" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="70">
-        <v>17</v>
-      </c>
-      <c r="E14" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="73"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="75"/>
-      <c r="N14" s="78"/>
-    </row>
-    <row r="15" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="68">
-        <v>3</v>
-      </c>
-      <c r="C15" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="70">
-        <v>18</v>
-      </c>
-      <c r="E15" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="G15" s="72">
-        <v>29</v>
-      </c>
-      <c r="H15" s="76">
-        <v>1.99</v>
-      </c>
-      <c r="I15" s="75">
-        <v>1.79</v>
-      </c>
-      <c r="J15" s="76">
-        <v>1.88</v>
-      </c>
-      <c r="K15" s="75">
-        <v>1.94</v>
-      </c>
-      <c r="L15" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" s="78"/>
-    </row>
-    <row r="16" spans="1:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="68">
-        <v>3</v>
-      </c>
-      <c r="C16" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="70">
-        <v>19</v>
-      </c>
-      <c r="E16" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="73" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="75">
-        <v>27</v>
-      </c>
-      <c r="H16" s="52">
-        <v>1.85</v>
-      </c>
-      <c r="I16" s="75">
-        <v>1.86</v>
-      </c>
-      <c r="J16" s="76">
-        <v>1.79</v>
-      </c>
-      <c r="K16" s="75">
-        <v>1.56</v>
-      </c>
-      <c r="L16" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="78"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="68">
-        <v>3</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="70">
-        <v>20</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="73"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="71"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="68">
-        <v>4</v>
-      </c>
-      <c r="C18" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="70">
-        <v>23</v>
-      </c>
-      <c r="E18" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="73"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="78"/>
-    </row>
-    <row r="19" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="68">
-        <v>4</v>
-      </c>
-      <c r="C19" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="70">
-        <v>26</v>
-      </c>
-      <c r="E19" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="73" t="s">
-        <v>117</v>
-      </c>
-      <c r="G19" s="75"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="75"/>
-      <c r="N19" s="78"/>
-    </row>
-    <row r="20" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="68">
-        <v>4</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="70">
-        <v>30</v>
-      </c>
-      <c r="E20" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="73" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="75">
-        <v>48</v>
-      </c>
-      <c r="H20" s="76">
-        <v>1.41</v>
-      </c>
-      <c r="I20" s="75">
-        <v>1.37</v>
-      </c>
-      <c r="J20" s="76">
-        <v>1.37</v>
-      </c>
-      <c r="K20" s="75">
-        <v>1.67</v>
-      </c>
-      <c r="L20" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="M20" s="72" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" s="75"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="68">
-        <v>4</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="70">
-        <v>31</v>
-      </c>
-      <c r="E21" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="73"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="76"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="75"/>
-      <c r="N21" s="78"/>
-    </row>
-    <row r="22" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="68">
-        <v>5</v>
-      </c>
-      <c r="C22" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="70">
-        <v>36</v>
-      </c>
-      <c r="E22" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="G22" s="75">
-        <v>20</v>
-      </c>
-      <c r="H22" s="76">
-        <v>0.51</v>
-      </c>
-      <c r="I22" s="75">
-        <v>0.44</v>
-      </c>
-      <c r="J22" s="76">
-        <v>0.51</v>
-      </c>
-      <c r="K22" s="75">
-        <v>0.44</v>
-      </c>
-      <c r="L22" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22" s="78"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="68">
-        <v>5</v>
-      </c>
-      <c r="C23" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="70">
-        <v>37</v>
-      </c>
-      <c r="E23" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="73"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="75"/>
-      <c r="N23" s="78"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="68">
-        <v>5</v>
-      </c>
-      <c r="C24" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="70">
-        <v>38</v>
-      </c>
-      <c r="E24" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="73"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="78"/>
-    </row>
-    <row r="25" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="68">
-        <v>5</v>
-      </c>
-      <c r="C25" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="70">
-        <v>40</v>
-      </c>
-      <c r="E25" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="73" t="s">
-        <v>120</v>
-      </c>
-      <c r="G25" s="75">
-        <v>44</v>
-      </c>
-      <c r="H25" s="76">
-        <v>1.04</v>
-      </c>
-      <c r="I25" s="75">
-        <v>1.06</v>
-      </c>
-      <c r="J25" s="76">
-        <v>1.08</v>
-      </c>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="M25" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="N25" s="78"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="68">
-        <v>5</v>
-      </c>
-      <c r="C26" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="70">
-        <v>43</v>
-      </c>
-      <c r="E26" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="73"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="76"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="76"/>
-      <c r="M26" s="75"/>
-      <c r="N26" s="78"/>
-    </row>
-    <row r="27" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="68">
-        <v>5</v>
-      </c>
-      <c r="C27" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="70">
-        <v>44</v>
-      </c>
-      <c r="E27" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="75">
-        <v>35</v>
-      </c>
-      <c r="H27" s="76">
-        <v>0.62</v>
-      </c>
-      <c r="I27" s="75">
-        <v>0.59</v>
-      </c>
-      <c r="J27" s="76">
-        <v>0.53</v>
-      </c>
-      <c r="K27" s="75">
-        <v>0.64</v>
-      </c>
-      <c r="L27" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M27" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N27" s="78"/>
-    </row>
-    <row r="28" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="68">
-        <v>6</v>
-      </c>
-      <c r="C28" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="70">
-        <v>47</v>
-      </c>
-      <c r="E28" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="73" t="s">
-        <v>122</v>
-      </c>
-      <c r="G28" s="75"/>
-      <c r="H28" s="76">
-        <v>2.74</v>
-      </c>
-      <c r="I28" s="75">
-        <v>3.47</v>
-      </c>
-      <c r="J28" s="76">
-        <v>3.14</v>
-      </c>
-      <c r="K28" s="75">
-        <v>3.3</v>
-      </c>
-      <c r="L28" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M28" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N28" s="78"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="68">
-        <v>6</v>
-      </c>
-      <c r="C29" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="70">
-        <v>51</v>
-      </c>
-      <c r="E29" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="73"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="76"/>
-      <c r="K29" s="75"/>
-      <c r="L29" s="76"/>
-      <c r="M29" s="75"/>
-      <c r="N29" s="78"/>
-    </row>
-    <row r="30" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="68">
-        <v>6</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="70">
-        <v>52</v>
-      </c>
-      <c r="E30" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="73" t="s">
-        <v>123</v>
-      </c>
-      <c r="G30" s="79">
-        <v>12</v>
-      </c>
-      <c r="H30" s="80">
-        <v>0.27</v>
-      </c>
-      <c r="I30" s="79">
-        <v>0.26</v>
-      </c>
-      <c r="J30" s="80">
-        <v>0.4</v>
-      </c>
-      <c r="K30" s="79">
-        <v>0.44</v>
-      </c>
-      <c r="L30" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M30" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="N30" s="81"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="83">
-        <v>6</v>
-      </c>
-      <c r="C31" s="84" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="85">
-        <v>55</v>
-      </c>
-      <c r="E31" s="84" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="86"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="87"/>
-      <c r="N31" s="89"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C86517-B91B-4061-867D-8EB3BAD5F5CB}">
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L1" s="55" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="7">
-        <v>2</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="102"/>
-      <c r="H3" s="103">
-        <v>0.69</v>
-      </c>
-      <c r="I3" s="102">
-        <v>0.72</v>
-      </c>
-      <c r="J3" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="K3" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="L3" s="102" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="7">
-        <v>3</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="104"/>
-      <c r="H4" s="105">
-        <v>1.25</v>
-      </c>
-      <c r="I4" s="104">
-        <v>1.27</v>
-      </c>
-      <c r="J4" s="105">
-        <v>1.4</v>
-      </c>
-      <c r="K4" s="105">
-        <v>1.4</v>
-      </c>
-      <c r="L4" s="114">
-        <v>2410021</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="7">
-        <v>5</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="104"/>
-      <c r="H5" s="105">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="I5" s="104">
-        <v>0.44</v>
-      </c>
-      <c r="J5" s="105">
-        <v>0.21</v>
-      </c>
-      <c r="K5" s="105">
-        <v>0.21</v>
-      </c>
-      <c r="L5" s="102"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5">
-        <v>6</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="101"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5">
-        <v>7</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="106"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3">
-        <v>2</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="7">
-        <v>8</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="106"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3">
-        <v>2</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7">
-        <v>9</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="104"/>
-      <c r="H9" s="105">
-        <v>1.06</v>
-      </c>
-      <c r="I9" s="104">
-        <v>0.99</v>
-      </c>
-      <c r="J9" s="105">
-        <v>1.01</v>
-      </c>
-      <c r="K9" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="L9" s="106"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="3">
-        <v>2</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="7">
-        <v>10</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="G10" s="104"/>
-      <c r="H10" s="105">
-        <v>0.93</v>
-      </c>
-      <c r="I10" s="104">
-        <v>0.69</v>
-      </c>
-      <c r="J10" s="105">
-        <v>0.97</v>
-      </c>
-      <c r="K10" s="105">
-        <v>1.4</v>
-      </c>
-      <c r="L10" s="106"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3">
-        <v>2</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="5">
-        <v>11</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="106"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3">
-        <v>2</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="5">
-        <v>13</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="106"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3">
-        <v>2</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="5">
-        <v>14</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="106"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3">
-        <v>3</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5">
-        <v>17</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="106"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3">
-        <v>3</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="7">
-        <v>18</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="G15" s="103"/>
-      <c r="H15" s="102">
-        <v>1.99</v>
-      </c>
-      <c r="I15" s="105">
-        <v>1.79</v>
-      </c>
-      <c r="J15" s="102">
-        <v>1.88</v>
-      </c>
-      <c r="K15" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="L15" s="106"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3">
-        <v>3</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="7">
-        <v>19</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="29"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="103">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="I16" s="107">
-        <v>2</v>
-      </c>
-      <c r="J16" s="105">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K16" s="105">
-        <v>1.4</v>
-      </c>
-      <c r="L16" s="106"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3">
-        <v>3</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="5">
-        <v>20</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="29"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="103"/>
-      <c r="K17" s="102"/>
-      <c r="L17" s="101"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3">
-        <v>4</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="5">
-        <v>23</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="29"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="106"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="3">
-        <v>4</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="7">
-        <v>26</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="G19" s="104"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="106"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="3">
-        <v>4</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="7">
-        <v>30</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="104"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="3">
-        <v>4</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="5">
-        <v>31</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="29"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="106"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="3">
-        <v>5</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="7">
-        <v>36</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" s="104"/>
-      <c r="H22" s="105">
-        <v>0.71</v>
-      </c>
-      <c r="I22" s="104">
-        <v>0.54</v>
-      </c>
-      <c r="J22" s="105">
-        <v>0.52</v>
-      </c>
-      <c r="K22" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="L22" s="106"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="3">
-        <v>5</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="5">
-        <v>37</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="106"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="3">
-        <v>5</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="5">
-        <v>38</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="29"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="106"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="3">
-        <v>5</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="7">
-        <v>40</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="G25" s="104"/>
-      <c r="H25" s="105">
-        <v>0.88</v>
-      </c>
-      <c r="I25" s="104">
-        <v>0.87</v>
-      </c>
-      <c r="J25" s="105">
-        <v>0.9</v>
-      </c>
-      <c r="K25" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="L25" s="106"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="3">
-        <v>5</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="5">
-        <v>43</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="103"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="3">
-        <v>5</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="7">
-        <v>44</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="G27" s="104"/>
-      <c r="H27" s="105">
-        <v>0.49</v>
-      </c>
-      <c r="I27" s="104">
-        <v>0.48</v>
-      </c>
-      <c r="J27" s="104">
-        <v>0.5</v>
-      </c>
-      <c r="K27" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="L27" s="106"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="3">
-        <v>6</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="7">
-        <v>47</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="G28" s="104"/>
-      <c r="H28" s="105">
-        <v>0.8</v>
-      </c>
-      <c r="I28" s="104">
-        <v>0.9</v>
-      </c>
-      <c r="J28" s="105">
-        <v>1</v>
-      </c>
-      <c r="K28" s="105">
-        <v>1.4</v>
-      </c>
-      <c r="L28" s="106"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="3">
-        <v>6</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="5">
-        <v>51</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="29"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="105"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="106"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="3">
-        <v>6</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="7">
-        <v>52</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="29"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="109">
-        <v>0.67</v>
-      </c>
-      <c r="I30" s="108">
-        <v>0.8</v>
-      </c>
-      <c r="J30" s="109">
-        <v>0.64</v>
-      </c>
-      <c r="K30" s="102">
-        <v>0.65</v>
-      </c>
-      <c r="L30" s="110"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="35">
-        <v>6</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="37">
-        <v>55</v>
-      </c>
-      <c r="E31" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="38"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="111"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="105"/>
-      <c r="L31" s="113"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Datos_Modificados_Qca.xlsx
+++ b/Datos_Modificados_Qca.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\minicores\R_analisis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\minicores\Qca_Bruto\Minicores-Q.canariensis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFCC347-C061-4559-A5EC-B4648804A32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEFE34B-7B97-41AB-8595-D74D67505789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4410" yWindow="3630" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2Feb21" sheetId="1" r:id="rId1"/>
@@ -6347,7 +6347,7 @@
         <v>37</v>
       </c>
       <c r="K3">
-        <v>1.5271999999999999</v>
+        <v>1.6272</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -6383,7 +6383,7 @@
         <v>37</v>
       </c>
       <c r="K4" s="88">
-        <v>1.8148</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -6418,7 +6418,7 @@
         <v>37</v>
       </c>
       <c r="K5">
-        <v>0.55330000000000001</v>
+        <v>0.65329999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6453,7 +6453,7 @@
         <v>37</v>
       </c>
       <c r="K6">
-        <v>0.83250000000000002</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -6548,7 +6548,7 @@
         <v>37</v>
       </c>
       <c r="K9">
-        <v>1.7496</v>
+        <v>1.496</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -6568,13 +6568,13 @@
         <v>29</v>
       </c>
       <c r="F10">
-        <v>1.2177</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>1.2379</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>1.1483000000000001</v>
+        <v>1</v>
       </c>
       <c r="I10" s="12">
         <v>1.25</v>
@@ -6645,7 +6645,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="89">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">

--- a/Datos_Modificados_Qca.xlsx
+++ b/Datos_Modificados_Qca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\minicores\Qca_Bruto\Minicores-Q.canariensis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEFE34B-7B97-41AB-8595-D74D67505789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6F7C11-7EA0-4D57-8400-69FF8B76740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="3630" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-705" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2Feb21" sheetId="1" r:id="rId1"/>
@@ -3623,19 +3623,19 @@
       </c>
       <c r="E7" s="80"/>
       <c r="F7">
-        <v>1.4475</v>
+        <v>1.2</v>
       </c>
       <c r="G7">
-        <v>1.4475</v>
+        <v>1.1719999999999999</v>
       </c>
       <c r="H7">
-        <v>1.4475</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="I7" s="81">
         <v>1.4</v>
       </c>
       <c r="J7" s="87">
-        <v>0.67030000000000001</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -4343,7 +4343,7 @@
     <col min="1013" max="1021" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>1.2619</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>1.7709999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>5</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>1.841</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>8</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>0.3745</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>9</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>0.87570000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>10</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>0.60209999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>18</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>1.956</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>19</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>1.2251000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>26</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>0.74270000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>30</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>1.9516</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>36</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>0.45369999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>40</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>1.4204000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>44</v>
       </c>
@@ -4760,17 +4760,21 @@
         <v>0.503</v>
       </c>
       <c r="G14">
-        <v>0.503</v>
+        <v>0.51919999999999999</v>
       </c>
       <c r="H14">
         <v>0.503</v>
       </c>
       <c r="I14" s="12"/>
       <c r="J14">
-        <v>0.98640000000000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="K14">
+        <f>AVERAGE(F14:H14)/J14</f>
+        <v>0.70807799442896935</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>47</v>
       </c>
@@ -5339,6 +5343,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5489,7 +5494,7 @@
         <v>1.1156999999999999</v>
       </c>
       <c r="G5">
-        <v>1.0998000000000001</v>
+        <v>1.1021000000000001</v>
       </c>
       <c r="H5">
         <v>1.0919000000000001</v>
@@ -5498,7 +5503,7 @@
         <v>1.3</v>
       </c>
       <c r="J5">
-        <v>0.91569999999999996</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
@@ -5650,7 +5655,7 @@
       </c>
       <c r="I10" s="12"/>
       <c r="J10">
-        <v>0.61899999999999999</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
@@ -5919,19 +5924,19 @@
         <v>41</v>
       </c>
       <c r="F6">
-        <v>0.44579999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="G6">
         <v>0.44579999999999997</v>
       </c>
       <c r="H6">
-        <v>0.42309999999999998</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I6" s="12">
         <v>0.46</v>
       </c>
       <c r="J6">
-        <v>0.60489999999999999</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
@@ -11750,7 +11755,7 @@
         <v>37</v>
       </c>
       <c r="L7" s="87">
-        <v>0.67030000000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
